--- a/DECEMBER/OUTSTANDING FLOOR/VICKEL LAUNDRY DECEMBER OUTSTANDING.xlsx
+++ b/DECEMBER/OUTSTANDING FLOOR/VICKEL LAUNDRY DECEMBER OUTSTANDING.xlsx
@@ -1372,7 +1372,7 @@
     </row>
     <row r="2" s="2" customFormat="1" spans="1:4">
       <c r="A2" s="10">
-        <v>46357</v>
+        <v>45992</v>
       </c>
       <c r="B2" s="18" t="s">
         <v>4</v>
@@ -1387,7 +1387,7 @@
     </row>
     <row r="3" s="2" customFormat="1" spans="1:4">
       <c r="A3" s="10">
-        <v>46358</v>
+        <v>45993</v>
       </c>
       <c r="B3" s="18" t="s">
         <v>5</v>
@@ -1402,7 +1402,7 @@
     </row>
     <row r="4" s="2" customFormat="1" spans="1:4">
       <c r="A4" s="10">
-        <v>46359</v>
+        <v>45994</v>
       </c>
       <c r="B4" s="11" t="s">
         <v>6</v>
@@ -1415,7 +1415,7 @@
     </row>
     <row r="5" s="2" customFormat="1" spans="1:4">
       <c r="A5" s="10">
-        <v>46360</v>
+        <v>45995</v>
       </c>
       <c r="B5" s="18" t="s">
         <v>7</v>
@@ -1430,7 +1430,7 @@
     </row>
     <row r="6" s="2" customFormat="1" spans="1:4">
       <c r="A6" s="10">
-        <v>46361</v>
+        <v>45996</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>6</v>
@@ -1443,7 +1443,7 @@
     </row>
     <row r="7" s="2" customFormat="1" spans="1:4">
       <c r="A7" s="10">
-        <v>46362</v>
+        <v>45997</v>
       </c>
       <c r="B7" s="18" t="s">
         <v>8</v>
@@ -1458,7 +1458,7 @@
     </row>
     <row r="8" s="2" customFormat="1" spans="1:4">
       <c r="A8" s="10">
-        <v>46363</v>
+        <v>45998</v>
       </c>
       <c r="B8" s="11" t="s">
         <v>6</v>
@@ -1471,7 +1471,7 @@
     </row>
     <row r="9" s="2" customFormat="1" spans="1:4">
       <c r="A9" s="10">
-        <v>46364</v>
+        <v>45999</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>6</v>
@@ -1484,7 +1484,7 @@
     </row>
     <row r="10" s="2" customFormat="1" spans="1:4">
       <c r="A10" s="10">
-        <v>46365</v>
+        <v>46000</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>6</v>
@@ -1497,7 +1497,7 @@
     </row>
     <row r="11" s="2" customFormat="1" spans="1:4">
       <c r="A11" s="10">
-        <v>46366</v>
+        <v>46001</v>
       </c>
       <c r="B11" s="18" t="s">
         <v>9</v>
@@ -1512,7 +1512,7 @@
     </row>
     <row r="12" s="2" customFormat="1" spans="1:4">
       <c r="A12" s="10">
-        <v>46367</v>
+        <v>46002</v>
       </c>
       <c r="B12" s="18" t="s">
         <v>10</v>
@@ -1527,7 +1527,7 @@
     </row>
     <row r="13" s="2" customFormat="1" spans="1:4">
       <c r="A13" s="10">
-        <v>46368</v>
+        <v>46003</v>
       </c>
       <c r="B13" s="18" t="s">
         <v>11</v>
@@ -1542,7 +1542,7 @@
     </row>
     <row r="14" s="2" customFormat="1" spans="1:4">
       <c r="A14" s="10">
-        <v>46369</v>
+        <v>46004</v>
       </c>
       <c r="B14" s="11" t="s">
         <v>6</v>
@@ -1555,7 +1555,7 @@
     </row>
     <row r="15" s="2" customFormat="1" spans="1:4">
       <c r="A15" s="10">
-        <v>46370</v>
+        <v>46005</v>
       </c>
       <c r="B15" s="11" t="s">
         <v>6</v>
@@ -1568,7 +1568,7 @@
     </row>
     <row r="16" s="2" customFormat="1" spans="1:4">
       <c r="A16" s="10">
-        <v>46371</v>
+        <v>46006</v>
       </c>
       <c r="B16" s="18" t="s">
         <v>12</v>
@@ -1583,20 +1583,22 @@
     </row>
     <row r="17" s="2" customFormat="1" spans="1:4">
       <c r="A17" s="10">
-        <v>46372</v>
+        <v>46007</v>
       </c>
       <c r="B17" s="11" t="s">
         <v>6</v>
       </c>
       <c r="C17" s="12">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="D17" s="11"/>
+        <v>5</v>
+      </c>
+      <c r="D17" s="14">
+        <v>40000</v>
+      </c>
     </row>
     <row r="18" s="2" customFormat="1" spans="1:4">
       <c r="A18" s="10">
-        <v>46373</v>
+        <v>46008</v>
       </c>
       <c r="B18" s="11" t="s">
         <v>6</v>
@@ -1605,11 +1607,11 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="D18" s="11"/>
+      <c r="D18" s="14"/>
     </row>
     <row r="19" s="2" customFormat="1" spans="1:4">
       <c r="A19" s="10">
-        <v>46374</v>
+        <v>46009</v>
       </c>
       <c r="B19" s="18" t="s">
         <v>13</v>
@@ -1624,7 +1626,7 @@
     </row>
     <row r="20" s="2" customFormat="1" spans="1:4">
       <c r="A20" s="10">
-        <v>46375</v>
+        <v>46010</v>
       </c>
       <c r="B20" s="18" t="s">
         <v>14</v>
@@ -1639,7 +1641,7 @@
     </row>
     <row r="21" s="2" customFormat="1" spans="1:4">
       <c r="A21" s="10">
-        <v>46376</v>
+        <v>46011</v>
       </c>
       <c r="B21" s="11" t="s">
         <v>6</v>
@@ -1648,11 +1650,11 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="D21" s="11"/>
+      <c r="D21" s="14"/>
     </row>
     <row r="22" s="2" customFormat="1" spans="1:4">
       <c r="A22" s="10">
-        <v>46377</v>
+        <v>46012</v>
       </c>
       <c r="B22" s="11">
         <v>1452</v>
@@ -1667,7 +1669,7 @@
     </row>
     <row r="23" s="2" customFormat="1" spans="1:4">
       <c r="A23" s="10">
-        <v>46378</v>
+        <v>46013</v>
       </c>
       <c r="B23" s="18" t="s">
         <v>15</v>
@@ -1682,7 +1684,7 @@
     </row>
     <row r="24" s="2" customFormat="1" spans="1:4">
       <c r="A24" s="10">
-        <v>46379</v>
+        <v>46014</v>
       </c>
       <c r="B24" s="11">
         <v>1453</v>
@@ -1697,7 +1699,7 @@
     </row>
     <row r="25" s="2" customFormat="1" spans="1:4">
       <c r="A25" s="10">
-        <v>46380</v>
+        <v>46015</v>
       </c>
       <c r="B25" s="11">
         <v>1454</v>
@@ -1712,7 +1714,7 @@
     </row>
     <row r="26" s="2" customFormat="1" spans="1:4">
       <c r="A26" s="10">
-        <v>46381</v>
+        <v>46016</v>
       </c>
       <c r="B26" s="11">
         <v>1455</v>
@@ -1727,7 +1729,7 @@
     </row>
     <row r="27" s="2" customFormat="1" spans="1:4">
       <c r="A27" s="10">
-        <v>46382</v>
+        <v>46017</v>
       </c>
       <c r="B27" s="11">
         <v>1456</v>
@@ -1742,7 +1744,7 @@
     </row>
     <row r="28" s="2" customFormat="1" spans="1:4">
       <c r="A28" s="10">
-        <v>46383</v>
+        <v>46018</v>
       </c>
       <c r="B28" s="11">
         <v>1457</v>
@@ -1757,7 +1759,7 @@
     </row>
     <row r="29" s="2" customFormat="1" spans="1:4">
       <c r="A29" s="10">
-        <v>46384</v>
+        <v>46019</v>
       </c>
       <c r="B29" s="11">
         <v>1458</v>
@@ -1772,7 +1774,7 @@
     </row>
     <row r="30" s="2" customFormat="1" spans="1:4">
       <c r="A30" s="10">
-        <v>46385</v>
+        <v>46020</v>
       </c>
       <c r="B30" s="11">
         <v>1459</v>
@@ -1787,7 +1789,7 @@
     </row>
     <row r="31" s="2" customFormat="1" spans="1:4">
       <c r="A31" s="10">
-        <v>46386</v>
+        <v>46021</v>
       </c>
       <c r="B31" s="11">
         <v>1460</v>
@@ -1802,7 +1804,7 @@
     </row>
     <row r="32" s="2" customFormat="1" spans="1:4">
       <c r="A32" s="10">
-        <v>46387</v>
+        <v>46022</v>
       </c>
       <c r="B32" s="15">
         <v>1461</v>
@@ -1823,7 +1825,7 @@
       <c r="C33" s="16"/>
       <c r="D33" s="17">
         <f>SUM(D2:D32)</f>
-        <v>944000</v>
+        <v>984000</v>
       </c>
     </row>
   </sheetData>
